--- a/artfynd/A 8024-2022 artfynd.xlsx
+++ b/artfynd/A 8024-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,6 +920,388 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121916477</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57791</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mörkmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>697325</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6617903</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ingrid Ehnström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ingrid Ehnström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121908431</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57304</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102620</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hökuggla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Surnia ulula</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mörkmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>697211</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6617928</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Ekman Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Ekman Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121916470</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57304</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102620</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Hökuggla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Surnia ulula</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mörkmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>697325</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6617903</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ingrid Ehnström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ingrid Ehnström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8024-2022 artfynd.xlsx
+++ b/artfynd/A 8024-2022 artfynd.xlsx
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121916477</v>
+        <v>121908431</v>
       </c>
       <c r="B4" t="n">
-        <v>57791</v>
+        <v>57304</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,37 +934,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>102620</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697325</v>
+        <v>697211</v>
       </c>
       <c r="R4" t="n">
-        <v>6617903</v>
+        <v>6617928</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,19 +1039,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ingrid Ehnström</t>
+          <t>Eva Ekman Eriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ingrid Ehnström</t>
+          <t>Eva Ekman Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121908431</v>
+        <v>121916470</v>
       </c>
       <c r="B5" t="n">
         <v>57304</v>
@@ -1093,7 +1093,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697211</v>
+        <v>697325</v>
       </c>
       <c r="R5" t="n">
-        <v>6617928</v>
+        <v>6617903</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1148,12 +1148,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,22 +1163,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Ekman Eriksson</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Ekman Eriksson</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121916470</v>
+        <v>121916477</v>
       </c>
       <c r="B6" t="n">
-        <v>57304</v>
+        <v>57791</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1192,37 +1187,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102620</v>
+        <v>102999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1278,6 +1273,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 8024-2022 artfynd.xlsx
+++ b/artfynd/A 8024-2022 artfynd.xlsx
@@ -922,7 +922,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121908431</v>
+        <v>121916470</v>
       </c>
       <c r="B4" t="n">
         <v>57304</v>
@@ -964,7 +964,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697211</v>
+        <v>697325</v>
       </c>
       <c r="R4" t="n">
-        <v>6617928</v>
+        <v>6617903</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,12 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,22 +1034,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Ekman Eriksson</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Ekman Eriksson</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121916470</v>
+        <v>121916477</v>
       </c>
       <c r="B5" t="n">
-        <v>57304</v>
+        <v>57791</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,37 +1058,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102620</v>
+        <v>102999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1149,6 +1144,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121916477</v>
+        <v>121908431</v>
       </c>
       <c r="B6" t="n">
-        <v>57791</v>
+        <v>57304</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,37 +1187,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102999</v>
+        <v>102620</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697325</v>
+        <v>697211</v>
       </c>
       <c r="R6" t="n">
-        <v>6617903</v>
+        <v>6617928</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,12 +1292,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ingrid Ehnström</t>
+          <t>Eva Ekman Eriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ingrid Ehnström</t>
+          <t>Eva Ekman Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 8024-2022 artfynd.xlsx
+++ b/artfynd/A 8024-2022 artfynd.xlsx
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121916470</v>
+        <v>121916477</v>
       </c>
       <c r="B4" t="n">
-        <v>57304</v>
+        <v>57791</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,37 +934,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102620</v>
+        <v>102999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1020,6 +1020,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121916477</v>
+        <v>121908431</v>
       </c>
       <c r="B5" t="n">
-        <v>57791</v>
+        <v>57304</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,37 +1063,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102999</v>
+        <v>102620</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1098,13 +1103,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697325</v>
+        <v>697211</v>
       </c>
       <c r="R5" t="n">
-        <v>6617903</v>
+        <v>6617928</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1143,12 +1148,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,19 +1168,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ingrid Ehnström</t>
+          <t>Eva Ekman Eriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ingrid Ehnström</t>
+          <t>Eva Ekman Eriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121908431</v>
+        <v>121916470</v>
       </c>
       <c r="B6" t="n">
         <v>57304</v>
@@ -1217,7 +1222,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1227,13 +1232,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697211</v>
+        <v>697325</v>
       </c>
       <c r="R6" t="n">
-        <v>6617928</v>
+        <v>6617903</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1267,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,12 +1277,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,12 +1292,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Ekman Eriksson</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Ekman Eriksson</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 8024-2022 artfynd.xlsx
+++ b/artfynd/A 8024-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121734040</v>
       </c>
       <c r="B2" t="n">
-        <v>57304</v>
+        <v>57312</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>121751427</v>
       </c>
       <c r="B3" t="n">
-        <v>97069</v>
+        <v>97087</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>121916477</v>
       </c>
       <c r="B4" t="n">
-        <v>57791</v>
+        <v>57799</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121908431</v>
+        <v>121916470</v>
       </c>
       <c r="B5" t="n">
-        <v>57304</v>
+        <v>57312</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697211</v>
+        <v>697325</v>
       </c>
       <c r="R5" t="n">
-        <v>6617928</v>
+        <v>6617903</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1148,12 +1148,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,22 +1163,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Ekman Eriksson</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Ekman Eriksson</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121916470</v>
+        <v>121908431</v>
       </c>
       <c r="B6" t="n">
-        <v>57304</v>
+        <v>57312</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1222,7 +1217,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1232,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697325</v>
+        <v>697211</v>
       </c>
       <c r="R6" t="n">
-        <v>6617903</v>
+        <v>6617928</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1267,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1277,7 +1272,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,12 +1292,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ingrid Ehnström</t>
+          <t>Eva Ekman Eriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ingrid Ehnström</t>
+          <t>Eva Ekman Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 8024-2022 artfynd.xlsx
+++ b/artfynd/A 8024-2022 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>121751427</v>
       </c>
       <c r="B3" t="n">
-        <v>97087</v>
+        <v>97089</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121916470</v>
+        <v>121908431</v>
       </c>
       <c r="B5" t="n">
         <v>57312</v>
@@ -1093,7 +1093,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697325</v>
+        <v>697211</v>
       </c>
       <c r="R5" t="n">
-        <v>6617903</v>
+        <v>6617928</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1148,7 +1148,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,19 +1168,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ingrid Ehnström</t>
+          <t>Eva Ekman Eriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ingrid Ehnström</t>
+          <t>Eva Ekman Eriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121908431</v>
+        <v>121916470</v>
       </c>
       <c r="B6" t="n">
         <v>57312</v>
@@ -1217,7 +1222,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1227,13 +1232,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697211</v>
+        <v>697325</v>
       </c>
       <c r="R6" t="n">
-        <v>6617928</v>
+        <v>6617903</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1267,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,12 +1277,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,12 +1292,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Ekman Eriksson</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Ekman Eriksson</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 8024-2022 artfynd.xlsx
+++ b/artfynd/A 8024-2022 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>121751427</v>
       </c>
       <c r="B3" t="n">
-        <v>97089</v>
+        <v>97096</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121916477</v>
+        <v>121908431</v>
       </c>
       <c r="B4" t="n">
-        <v>57799</v>
+        <v>57312</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,37 +934,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>102620</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697325</v>
+        <v>697211</v>
       </c>
       <c r="R4" t="n">
-        <v>6617903</v>
+        <v>6617928</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,19 +1039,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ingrid Ehnström</t>
+          <t>Eva Ekman Eriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ingrid Ehnström</t>
+          <t>Eva Ekman Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121908431</v>
+        <v>121916470</v>
       </c>
       <c r="B5" t="n">
         <v>57312</v>
@@ -1093,7 +1093,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697211</v>
+        <v>697325</v>
       </c>
       <c r="R5" t="n">
-        <v>6617928</v>
+        <v>6617903</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1148,12 +1148,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,22 +1163,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Ekman Eriksson</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Ekman Eriksson</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121916470</v>
+        <v>121916477</v>
       </c>
       <c r="B6" t="n">
-        <v>57312</v>
+        <v>57799</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1192,37 +1187,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102620</v>
+        <v>102999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1278,6 +1273,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 8024-2022 artfynd.xlsx
+++ b/artfynd/A 8024-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1302,6 +1302,254 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122189140</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57316</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102620</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hökuggla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Surnia ulula</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vargbergen, Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>697197</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6617985</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Micael Söderman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Micael Söderman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122189142</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57285</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vargbergen, Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>697197</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6617985</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Micael Söderman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Micael Söderman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8024-2022 artfynd.xlsx
+++ b/artfynd/A 8024-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121734040</v>
       </c>
       <c r="B2" t="n">
-        <v>57312</v>
+        <v>57316</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>121751427</v>
       </c>
       <c r="B3" t="n">
-        <v>97096</v>
+        <v>97105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>121908431</v>
       </c>
       <c r="B4" t="n">
-        <v>57312</v>
+        <v>57316</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>121916470</v>
       </c>
       <c r="B5" t="n">
-        <v>57312</v>
+        <v>57316</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>121916477</v>
       </c>
       <c r="B6" t="n">
-        <v>57799</v>
+        <v>57803</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 8024-2022 artfynd.xlsx
+++ b/artfynd/A 8024-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121734040</v>
       </c>
       <c r="B2" t="n">
-        <v>57316</v>
+        <v>57319</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>121751427</v>
       </c>
       <c r="B3" t="n">
-        <v>97105</v>
+        <v>97113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>121908431</v>
       </c>
       <c r="B4" t="n">
-        <v>57316</v>
+        <v>57319</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>121916470</v>
       </c>
       <c r="B5" t="n">
-        <v>57316</v>
+        <v>57319</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>121916477</v>
       </c>
       <c r="B6" t="n">
-        <v>57803</v>
+        <v>57807</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>122189140</v>
       </c>
       <c r="B7" t="n">
-        <v>57316</v>
+        <v>57319</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>122189142</v>
       </c>
       <c r="B8" t="n">
-        <v>57285</v>
+        <v>57288</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 8024-2022 artfynd.xlsx
+++ b/artfynd/A 8024-2022 artfynd.xlsx
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121908431</v>
+        <v>121916470</v>
       </c>
       <c r="B4" t="n">
-        <v>57319</v>
+        <v>57321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697211</v>
+        <v>697325</v>
       </c>
       <c r="R4" t="n">
-        <v>6617928</v>
+        <v>6617903</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,12 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,22 +1034,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Ekman Eriksson</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Ekman Eriksson</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121916470</v>
+        <v>121916477</v>
       </c>
       <c r="B5" t="n">
-        <v>57319</v>
+        <v>57809</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,37 +1058,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102620</v>
+        <v>102999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1149,6 +1144,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121916477</v>
+        <v>121908431</v>
       </c>
       <c r="B6" t="n">
-        <v>57807</v>
+        <v>57321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,37 +1187,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102999</v>
+        <v>102620</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697325</v>
+        <v>697211</v>
       </c>
       <c r="R6" t="n">
-        <v>6617903</v>
+        <v>6617928</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,22 +1292,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ingrid Ehnström</t>
+          <t>Eva Ekman Eriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ingrid Ehnström</t>
+          <t>Eva Ekman Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122189140</v>
+        <v>122189142</v>
       </c>
       <c r="B7" t="n">
-        <v>57319</v>
+        <v>57290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,20 +1316,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102620</v>
+        <v>100067</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1346,7 +1346,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122189142</v>
+        <v>122189140</v>
       </c>
       <c r="B8" t="n">
-        <v>57288</v>
+        <v>57321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1440,20 +1440,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100067</v>
+        <v>102620</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1470,7 +1470,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>

--- a/artfynd/A 8024-2022 artfynd.xlsx
+++ b/artfynd/A 8024-2022 artfynd.xlsx
@@ -922,7 +922,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121916470</v>
+        <v>121908431</v>
       </c>
       <c r="B4" t="n">
         <v>57321</v>
@@ -964,7 +964,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697325</v>
+        <v>697211</v>
       </c>
       <c r="R4" t="n">
-        <v>6617903</v>
+        <v>6617928</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,22 +1039,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ingrid Ehnström</t>
+          <t>Eva Ekman Eriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ingrid Ehnström</t>
+          <t>Eva Ekman Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121916477</v>
+        <v>121916470</v>
       </c>
       <c r="B5" t="n">
-        <v>57809</v>
+        <v>57321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,37 +1063,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102999</v>
+        <v>102620</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1144,11 +1149,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121908431</v>
+        <v>121916477</v>
       </c>
       <c r="B6" t="n">
-        <v>57321</v>
+        <v>57809</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,37 +1187,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102620</v>
+        <v>102999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697211</v>
+        <v>697325</v>
       </c>
       <c r="R6" t="n">
-        <v>6617928</v>
+        <v>6617903</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,22 +1292,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Ekman Eriksson</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Ekman Eriksson</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122189142</v>
+        <v>122189140</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>57321</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,20 +1316,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100067</v>
+        <v>102620</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1346,7 +1346,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122189140</v>
+        <v>122189142</v>
       </c>
       <c r="B8" t="n">
-        <v>57321</v>
+        <v>57290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1440,20 +1440,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102620</v>
+        <v>100067</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1470,7 +1470,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>

--- a/artfynd/A 8024-2022 artfynd.xlsx
+++ b/artfynd/A 8024-2022 artfynd.xlsx
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121916477</v>
+        <v>121908431</v>
       </c>
       <c r="B4" t="n">
-        <v>57809</v>
+        <v>57321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,37 +934,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>102620</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697325</v>
+        <v>697211</v>
       </c>
       <c r="R4" t="n">
-        <v>6617903</v>
+        <v>6617928</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,19 +1039,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ingrid Ehnström</t>
+          <t>Eva Ekman Eriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ingrid Ehnström</t>
+          <t>Eva Ekman Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121908431</v>
+        <v>121916470</v>
       </c>
       <c r="B5" t="n">
         <v>57321</v>
@@ -1093,7 +1093,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697211</v>
+        <v>697325</v>
       </c>
       <c r="R5" t="n">
-        <v>6617928</v>
+        <v>6617903</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1148,12 +1148,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Satt i grantopp i östta kanten på hygget, sågs från vändplanen/vändslingan utefter traktorvägen.  Söder om Vargbergen och norr om sjön Skären, Riala.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,22 +1163,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Ekman Eriksson</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Ekman Eriksson</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121916470</v>
+        <v>121916477</v>
       </c>
       <c r="B6" t="n">
-        <v>57321</v>
+        <v>57809</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1192,37 +1187,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102620</v>
+        <v>102999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1278,6 +1273,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1304,10 +1304,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122189140</v>
+        <v>122189142</v>
       </c>
       <c r="B7" t="n">
-        <v>57321</v>
+        <v>57290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,20 +1316,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102620</v>
+        <v>100067</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1346,7 +1346,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122189142</v>
+        <v>122189140</v>
       </c>
       <c r="B8" t="n">
-        <v>57290</v>
+        <v>57321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1440,20 +1440,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100067</v>
+        <v>102620</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1470,7 +1470,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>

--- a/artfynd/A 8024-2022 artfynd.xlsx
+++ b/artfynd/A 8024-2022 artfynd.xlsx
@@ -1304,10 +1304,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122189142</v>
+        <v>122189140</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>57326</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,20 +1316,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100067</v>
+        <v>102620</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1346,7 +1346,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122189140</v>
+        <v>122189142</v>
       </c>
       <c r="B8" t="n">
-        <v>57321</v>
+        <v>57295</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1440,20 +1440,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102620</v>
+        <v>100067</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1470,7 +1470,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>

--- a/artfynd/A 8024-2022 artfynd.xlsx
+++ b/artfynd/A 8024-2022 artfynd.xlsx
@@ -1304,10 +1304,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122189140</v>
+        <v>122189142</v>
       </c>
       <c r="B7" t="n">
-        <v>57326</v>
+        <v>57295</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,20 +1316,15 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102620</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Hökuggla</t>
-        </is>
+        <v>100067</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1346,7 +1341,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1428,10 +1423,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122189142</v>
+        <v>122189140</v>
       </c>
       <c r="B8" t="n">
-        <v>57295</v>
+        <v>57326</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1440,20 +1435,15 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100067</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Havsörn</t>
-        </is>
+        <v>102620</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1470,7 +1460,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>

--- a/artfynd/A 8024-2022 artfynd.xlsx
+++ b/artfynd/A 8024-2022 artfynd.xlsx
@@ -1307,7 +1307,7 @@
         <v>122189142</v>
       </c>
       <c r="B7" t="n">
-        <v>57295</v>
+        <v>57299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,6 +1321,11 @@
       </c>
       <c r="E7" t="n">
         <v>100067</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1426,7 +1431,7 @@
         <v>122189140</v>
       </c>
       <c r="B8" t="n">
-        <v>57326</v>
+        <v>57330</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1440,6 +1445,11 @@
       </c>
       <c r="E8" t="n">
         <v>102620</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Hökuggla</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>

--- a/artfynd/A 8024-2022 artfynd.xlsx
+++ b/artfynd/A 8024-2022 artfynd.xlsx
@@ -1304,10 +1304,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122189142</v>
+        <v>122189140</v>
       </c>
       <c r="B7" t="n">
-        <v>57299</v>
+        <v>57330</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,20 +1316,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100067</v>
+        <v>102620</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1346,7 +1346,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122189140</v>
+        <v>122189142</v>
       </c>
       <c r="B8" t="n">
-        <v>57330</v>
+        <v>57299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1440,20 +1440,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102620</v>
+        <v>100067</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1470,7 +1470,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
